--- a/Output Files Gemini 3.5 Flash/Example-Guided_LLM_Scoring_results_run_02.xlsx
+++ b/Output Files Gemini 3.5 Flash/Example-Guided_LLM_Scoring_results_run_02.xlsx
@@ -510,8 +510,6 @@
       <c r="E2" t="n">
         <v>92</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>72</t>
@@ -558,8 +556,6 @@
       <c r="E3" t="n">
         <v>92</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>76</t>
@@ -606,8 +602,6 @@
       <c r="E4" t="n">
         <v>92</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>80</t>
@@ -654,8 +648,6 @@
       <c r="E5" t="n">
         <v>20</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>68</t>
@@ -702,8 +694,6 @@
       <c r="E6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>71</t>
@@ -750,8 +740,6 @@
       <c r="E7" t="n">
         <v>20</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>74</t>
@@ -798,8 +786,6 @@
       <c r="E8" t="n">
         <v>90</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>77</t>
@@ -846,8 +832,6 @@
       <c r="E9" t="n">
         <v>90</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>80</t>
@@ -894,8 +878,6 @@
       <c r="E10" t="n">
         <v>90</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>83</t>
@@ -942,8 +924,6 @@
       <c r="E11" t="n">
         <v>22</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>65</t>
@@ -990,8 +970,6 @@
       <c r="E12" t="n">
         <v>22</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>68</t>
@@ -1038,8 +1016,6 @@
       <c r="E13" t="n">
         <v>22</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>71</t>
@@ -1086,8 +1062,6 @@
       <c r="E14" t="n">
         <v>86</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>74</t>
@@ -1134,8 +1108,6 @@
       <c r="E15" t="n">
         <v>86</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>77</t>
@@ -1182,8 +1154,6 @@
       <c r="E16" t="n">
         <v>86</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>80</t>
@@ -1230,8 +1200,6 @@
       <c r="E17" t="n">
         <v>93</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>78</t>
@@ -1278,8 +1246,6 @@
       <c r="E18" t="n">
         <v>93</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>81</t>
@@ -1326,8 +1292,6 @@
       <c r="E19" t="n">
         <v>93</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>84</t>
@@ -1374,8 +1338,6 @@
       <c r="E20" t="n">
         <v>24</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>64</t>
@@ -1422,8 +1384,6 @@
       <c r="E21" t="n">
         <v>24</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>67</t>
@@ -1470,8 +1430,6 @@
       <c r="E22" t="n">
         <v>24</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>70</t>
@@ -1518,8 +1476,6 @@
       <c r="E23" t="n">
         <v>89</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>76</t>
@@ -1566,8 +1522,6 @@
       <c r="E24" t="n">
         <v>89</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>79</t>
@@ -1614,8 +1568,6 @@
       <c r="E25" t="n">
         <v>89</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>82</t>
@@ -1662,8 +1614,6 @@
       <c r="E26" t="n">
         <v>26</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>67</t>
@@ -1710,8 +1660,6 @@
       <c r="E27" t="n">
         <v>26</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>70</t>
@@ -1758,8 +1706,6 @@
       <c r="E28" t="n">
         <v>26</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>73</t>
@@ -1806,8 +1752,6 @@
       <c r="E29" t="n">
         <v>19</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>68</t>
@@ -1854,8 +1798,6 @@
       <c r="E30" t="n">
         <v>19</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>71</t>
@@ -1902,8 +1844,6 @@
       <c r="E31" t="n">
         <v>19</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>74</t>
@@ -1950,8 +1890,6 @@
       <c r="E32" t="n">
         <v>90</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>76</t>
@@ -1998,8 +1936,6 @@
       <c r="E33" t="n">
         <v>90</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>79</t>
@@ -2046,8 +1982,6 @@
       <c r="E34" t="n">
         <v>90</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>82</t>
@@ -2094,8 +2028,6 @@
       <c r="E35" t="n">
         <v>21</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>66</t>
@@ -2142,8 +2074,6 @@
       <c r="E36" t="n">
         <v>21</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>69</t>
@@ -2190,8 +2120,6 @@
       <c r="E37" t="n">
         <v>21</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>72</t>
@@ -2238,8 +2166,6 @@
       <c r="E38" t="n">
         <v>94</v>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>76</t>
@@ -2286,8 +2212,6 @@
       <c r="E39" t="n">
         <v>94</v>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>79</t>
@@ -2334,8 +2258,6 @@
       <c r="E40" t="n">
         <v>94</v>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>82</t>
@@ -2382,8 +2304,6 @@
       <c r="E41" t="n">
         <v>88</v>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>73</t>
@@ -2430,8 +2350,6 @@
       <c r="E42" t="n">
         <v>88</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>76</t>
@@ -2478,8 +2396,6 @@
       <c r="E43" t="n">
         <v>88</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>79</t>
@@ -2526,8 +2442,6 @@
       <c r="E44" t="n">
         <v>92</v>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>78</t>
@@ -2574,8 +2488,6 @@
       <c r="E45" t="n">
         <v>92</v>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>81</t>
@@ -2622,8 +2534,6 @@
       <c r="E46" t="n">
         <v>92</v>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>84</t>
@@ -2670,8 +2580,6 @@
       <c r="E47" t="n">
         <v>20</v>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>65</t>
@@ -2718,8 +2626,6 @@
       <c r="E48" t="n">
         <v>20</v>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>68</t>
@@ -2766,8 +2672,6 @@
       <c r="E49" t="n">
         <v>20</v>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>71</t>
@@ -2814,8 +2718,6 @@
       <c r="E50" t="n">
         <v>84</v>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>75</t>
@@ -2862,8 +2764,6 @@
       <c r="E51" t="n">
         <v>84</v>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>78</t>
@@ -2910,8 +2810,6 @@
       <c r="E52" t="n">
         <v>84</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>81</t>
@@ -2958,8 +2856,6 @@
       <c r="E53" t="n">
         <v>91</v>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>78</t>
@@ -3006,8 +2902,6 @@
       <c r="E54" t="n">
         <v>91</v>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>81</t>
@@ -3054,8 +2948,6 @@
       <c r="E55" t="n">
         <v>91</v>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>84</t>
@@ -3102,8 +2994,6 @@
       <c r="E56" t="n">
         <v>90</v>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>71</t>
@@ -3150,8 +3040,6 @@
       <c r="E57" t="n">
         <v>90</v>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>75</t>
@@ -3198,8 +3086,6 @@
       <c r="E58" t="n">
         <v>90</v>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>79</t>
@@ -3246,8 +3132,6 @@
       <c r="E59" t="n">
         <v>18</v>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>66</t>
@@ -3294,8 +3178,6 @@
       <c r="E60" t="n">
         <v>18</v>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>69</t>
@@ -3342,8 +3224,6 @@
       <c r="E61" t="n">
         <v>18</v>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>72</t>
@@ -3390,8 +3270,6 @@
       <c r="E62" t="n">
         <v>22</v>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>65</t>
@@ -3438,8 +3316,6 @@
       <c r="E63" t="n">
         <v>22</v>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>68</t>
@@ -3486,8 +3362,6 @@
       <c r="E64" t="n">
         <v>22</v>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>71</t>
@@ -3534,8 +3408,6 @@
       <c r="E65" t="n">
         <v>87</v>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>75</t>
@@ -3582,8 +3454,6 @@
       <c r="E66" t="n">
         <v>87</v>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>78</t>
@@ -3630,8 +3500,6 @@
       <c r="E67" t="n">
         <v>87</v>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>81</t>
@@ -3678,8 +3546,6 @@
       <c r="E68" t="n">
         <v>19</v>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>66</t>
@@ -3726,8 +3592,6 @@
       <c r="E69" t="n">
         <v>19</v>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>69</t>
@@ -3774,8 +3638,6 @@
       <c r="E70" t="n">
         <v>19</v>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>72</t>
@@ -3822,8 +3684,6 @@
       <c r="E71" t="n">
         <v>90</v>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>78</t>
@@ -3870,8 +3730,6 @@
       <c r="E72" t="n">
         <v>90</v>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>81</t>
@@ -3918,8 +3776,6 @@
       <c r="E73" t="n">
         <v>90</v>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>84</t>
@@ -3966,8 +3822,6 @@
       <c r="E74" t="n">
         <v>91</v>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>76</t>
@@ -4014,8 +3868,6 @@
       <c r="E75" t="n">
         <v>91</v>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>79</t>
@@ -4062,8 +3914,6 @@
       <c r="E76" t="n">
         <v>91</v>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>82</t>
@@ -4110,8 +3960,6 @@
       <c r="E77" t="n">
         <v>17</v>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>66</t>
@@ -4158,8 +4006,6 @@
       <c r="E78" t="n">
         <v>17</v>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>69</t>
@@ -4206,8 +4052,6 @@
       <c r="E79" t="n">
         <v>17</v>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>72</t>
@@ -4254,8 +4098,6 @@
       <c r="E80" t="n">
         <v>21</v>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>66</t>
@@ -4302,8 +4144,6 @@
       <c r="E81" t="n">
         <v>21</v>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>69</t>
@@ -4350,8 +4190,6 @@
       <c r="E82" t="n">
         <v>21</v>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>72</t>
@@ -4398,8 +4236,6 @@
       <c r="E83" t="n">
         <v>98</v>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>78</t>
@@ -4446,8 +4282,6 @@
       <c r="E84" t="n">
         <v>98</v>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>80</t>
@@ -4494,8 +4328,6 @@
       <c r="E85" t="n">
         <v>98</v>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>82</t>
@@ -4542,8 +4374,6 @@
       <c r="E86" t="n">
         <v>97</v>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>79</t>
@@ -4590,8 +4420,6 @@
       <c r="E87" t="n">
         <v>97</v>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>81</t>
@@ -4638,8 +4466,6 @@
       <c r="E88" t="n">
         <v>97</v>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>83</t>
@@ -4686,8 +4512,6 @@
       <c r="E89" t="n">
         <v>91</v>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>77</t>
@@ -4734,8 +4558,6 @@
       <c r="E90" t="n">
         <v>91</v>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>79</t>
@@ -4782,8 +4604,6 @@
       <c r="E91" t="n">
         <v>91</v>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>81</t>
@@ -4830,8 +4650,6 @@
       <c r="E92" t="n">
         <v>91</v>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>82</t>
@@ -4878,8 +4696,6 @@
       <c r="E93" t="n">
         <v>91</v>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>76</t>
@@ -4926,8 +4742,6 @@
       <c r="E94" t="n">
         <v>91</v>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>70</t>
@@ -4974,8 +4788,6 @@
       <c r="E95" t="n">
         <v>102</v>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>78</t>
@@ -5022,8 +4834,6 @@
       <c r="E96" t="n">
         <v>102</v>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>80</t>
@@ -5070,8 +4880,6 @@
       <c r="E97" t="n">
         <v>102</v>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>82</t>
@@ -5118,8 +4926,6 @@
       <c r="E98" t="n">
         <v>94</v>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>79</t>
@@ -5166,8 +4972,6 @@
       <c r="E99" t="n">
         <v>94</v>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>81</t>
@@ -5214,8 +5018,6 @@
       <c r="E100" t="n">
         <v>94</v>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>83</t>
@@ -5262,8 +5064,6 @@
       <c r="E101" t="n">
         <v>89</v>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>78</t>
@@ -5310,8 +5110,6 @@
       <c r="E102" t="n">
         <v>89</v>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>80</t>
@@ -5358,8 +5156,6 @@
       <c r="E103" t="n">
         <v>89</v>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>82</t>
@@ -5406,8 +5202,6 @@
       <c r="E104" t="n">
         <v>15</v>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>60</t>
@@ -5454,8 +5248,6 @@
       <c r="E105" t="n">
         <v>15</v>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>63</t>
@@ -5502,8 +5294,6 @@
       <c r="E106" t="n">
         <v>15</v>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>67</t>
@@ -5550,8 +5340,6 @@
       <c r="E107" t="n">
         <v>78</v>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>73</t>
@@ -5598,8 +5386,6 @@
       <c r="E108" t="n">
         <v>78</v>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>76</t>
@@ -5646,8 +5432,6 @@
       <c r="E109" t="n">
         <v>78</v>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>79</t>
@@ -5694,8 +5478,6 @@
       <c r="E110" t="n">
         <v>82</v>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>74</t>
@@ -5742,8 +5524,6 @@
       <c r="E111" t="n">
         <v>82</v>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>78</t>
@@ -5790,8 +5570,6 @@
       <c r="E112" t="n">
         <v>82</v>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>80</t>
@@ -5838,8 +5616,6 @@
       <c r="E113" t="n">
         <v>48</v>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>66</t>
@@ -5886,8 +5662,6 @@
       <c r="E114" t="n">
         <v>48</v>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>69</t>
@@ -5934,8 +5708,6 @@
       <c r="E115" t="n">
         <v>48</v>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>72</t>
@@ -5982,8 +5754,6 @@
       <c r="E116" t="n">
         <v>42</v>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>65</t>
@@ -6030,8 +5800,6 @@
       <c r="E117" t="n">
         <v>42</v>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>68</t>
@@ -6078,8 +5846,6 @@
       <c r="E118" t="n">
         <v>42</v>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>72</t>
@@ -6126,8 +5892,6 @@
       <c r="E119" t="n">
         <v>40</v>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>66</t>
@@ -6174,8 +5938,6 @@
       <c r="E120" t="n">
         <v>40</v>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>70</t>
@@ -6222,8 +5984,6 @@
       <c r="E121" t="n">
         <v>40</v>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>74</t>
@@ -6270,8 +6030,6 @@
       <c r="E122" t="n">
         <v>95</v>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>71</t>
@@ -6318,8 +6076,6 @@
       <c r="E123" t="n">
         <v>95</v>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>76</t>
@@ -6366,8 +6122,6 @@
       <c r="E124" t="n">
         <v>95</v>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>82</t>
@@ -6414,8 +6168,6 @@
       <c r="E125" t="n">
         <v>22</v>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>65</t>
@@ -6462,8 +6214,6 @@
       <c r="E126" t="n">
         <v>22</v>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>70</t>
@@ -6510,8 +6260,6 @@
       <c r="E127" t="n">
         <v>22</v>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>76</t>
@@ -6558,8 +6306,6 @@
       <c r="E128" t="n">
         <v>92</v>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>78</t>
@@ -6606,8 +6352,6 @@
       <c r="E129" t="n">
         <v>92</v>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>85</t>
@@ -6654,8 +6398,6 @@
       <c r="E130" t="n">
         <v>92</v>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>Off</t>
@@ -6702,8 +6444,6 @@
       <c r="E131" t="n">
         <v>88</v>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>78</t>
@@ -6750,8 +6490,6 @@
       <c r="E132" t="n">
         <v>88</v>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>85</t>
@@ -6798,8 +6536,6 @@
       <c r="E133" t="n">
         <v>88</v>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>Off</t>
@@ -6846,8 +6582,6 @@
       <c r="E134" t="n">
         <v>84</v>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>73</t>
@@ -6894,8 +6628,6 @@
       <c r="E135" t="n">
         <v>84</v>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>77</t>
@@ -6942,8 +6674,6 @@
       <c r="E136" t="n">
         <v>84</v>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>80</t>
@@ -6990,8 +6720,6 @@
       <c r="E137" t="n">
         <v>12</v>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>65</t>
@@ -7038,8 +6766,6 @@
       <c r="E138" t="n">
         <v>12</v>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>68</t>
@@ -7086,8 +6812,6 @@
       <c r="E139" t="n">
         <v>12</v>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>72</t>
@@ -7134,8 +6858,6 @@
       <c r="E140" t="n">
         <v>20</v>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>66</t>
@@ -7182,8 +6904,6 @@
       <c r="E141" t="n">
         <v>20</v>
       </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>70</t>
@@ -7230,8 +6950,6 @@
       <c r="E142" t="n">
         <v>20</v>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>73</t>
@@ -7278,8 +6996,6 @@
       <c r="E143" t="n">
         <v>22</v>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>67</t>
@@ -7326,8 +7042,6 @@
       <c r="E144" t="n">
         <v>22</v>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>70</t>
@@ -7374,8 +7088,6 @@
       <c r="E145" t="n">
         <v>22</v>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>75</t>
@@ -7422,8 +7134,6 @@
       <c r="E146" t="n">
         <v>28</v>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>66</t>
@@ -7470,8 +7180,6 @@
       <c r="E147" t="n">
         <v>28</v>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>69</t>
@@ -7518,8 +7226,6 @@
       <c r="E148" t="n">
         <v>28</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>73</t>
@@ -7566,8 +7272,6 @@
       <c r="E149" t="n">
         <v>94</v>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>70</t>
@@ -7614,8 +7318,6 @@
       <c r="E150" t="n">
         <v>94</v>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>75</t>
@@ -7662,8 +7364,6 @@
       <c r="E151" t="n">
         <v>94</v>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>80</t>
@@ -7710,8 +7410,6 @@
       <c r="E152" t="n">
         <v>91</v>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>74</t>
@@ -7758,8 +7456,6 @@
       <c r="E153" t="n">
         <v>91</v>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>78</t>
@@ -7806,8 +7502,6 @@
       <c r="E154" t="n">
         <v>91</v>
       </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>82</t>
@@ -7854,8 +7548,6 @@
       <c r="E155" t="n">
         <v>68</v>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>68</t>
@@ -7902,8 +7594,6 @@
       <c r="E156" t="n">
         <v>68</v>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>70</t>
@@ -7950,8 +7640,6 @@
       <c r="E157" t="n">
         <v>68</v>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>72</t>
@@ -7998,8 +7686,6 @@
       <c r="E158" t="n">
         <v>8</v>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>66</t>
@@ -8046,8 +7732,6 @@
       <c r="E159" t="n">
         <v>8</v>
       </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>69</t>
@@ -8094,8 +7778,6 @@
       <c r="E160" t="n">
         <v>8</v>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>72</t>
@@ -8142,8 +7824,6 @@
       <c r="E161" t="n">
         <v>42</v>
       </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>65</t>
@@ -8190,8 +7870,6 @@
       <c r="E162" t="n">
         <v>42</v>
       </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>68</t>
@@ -8238,8 +7916,6 @@
       <c r="E163" t="n">
         <v>42</v>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>71</t>
@@ -8286,8 +7962,6 @@
       <c r="E164" t="n">
         <v>68</v>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>66</t>
@@ -8334,8 +8008,6 @@
       <c r="E165" t="n">
         <v>68</v>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>72</t>
@@ -8382,8 +8054,6 @@
       <c r="E166" t="n">
         <v>68</v>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>78</t>
@@ -8430,8 +8100,6 @@
       <c r="E167" t="n">
         <v>78</v>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>72</t>
@@ -8478,8 +8146,6 @@
       <c r="E168" t="n">
         <v>78</v>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>76</t>
@@ -8526,8 +8192,6 @@
       <c r="E169" t="n">
         <v>78</v>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>79</t>
@@ -8574,8 +8238,6 @@
       <c r="E170" t="n">
         <v>96</v>
       </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>72</t>
@@ -8622,8 +8284,6 @@
       <c r="E171" t="n">
         <v>96</v>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>76</t>
@@ -8670,8 +8330,6 @@
       <c r="E172" t="n">
         <v>96</v>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>80</t>
@@ -8718,8 +8376,6 @@
       <c r="E173" t="n">
         <v>90</v>
       </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
           <t>73</t>
@@ -8766,8 +8422,6 @@
       <c r="E174" t="n">
         <v>90</v>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>77</t>
@@ -8814,8 +8468,6 @@
       <c r="E175" t="n">
         <v>90</v>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>81</t>
@@ -8862,8 +8514,6 @@
       <c r="E176" t="n">
         <v>29</v>
       </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>62</t>
@@ -8910,8 +8560,6 @@
       <c r="E177" t="n">
         <v>29</v>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>66</t>
@@ -8958,8 +8606,6 @@
       <c r="E178" t="n">
         <v>29</v>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>69</t>
@@ -9006,8 +8652,6 @@
       <c r="E179" t="n">
         <v>24</v>
       </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>66</t>
@@ -9054,8 +8698,6 @@
       <c r="E180" t="n">
         <v>24</v>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>69</t>
@@ -9102,8 +8744,6 @@
       <c r="E181" t="n">
         <v>24</v>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>72</t>
@@ -9150,8 +8790,6 @@
       <c r="E182" t="n">
         <v>25</v>
       </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>64</t>
@@ -9198,8 +8836,6 @@
       <c r="E183" t="n">
         <v>25</v>
       </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>67</t>
@@ -9246,8 +8882,6 @@
       <c r="E184" t="n">
         <v>25</v>
       </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>70</t>
@@ -9294,8 +8928,6 @@
       <c r="E185" t="n">
         <v>18</v>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>62</t>
@@ -9342,8 +8974,6 @@
       <c r="E186" t="n">
         <v>18</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>65</t>
@@ -9390,8 +9020,6 @@
       <c r="E187" t="n">
         <v>18</v>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
           <t>68</t>
@@ -9438,8 +9066,6 @@
       <c r="E188" t="n">
         <v>14</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>58</t>
@@ -9486,8 +9112,6 @@
       <c r="E189" t="n">
         <v>14</v>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>61</t>
@@ -9534,8 +9158,6 @@
       <c r="E190" t="n">
         <v>14</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>64</t>
@@ -9582,8 +9204,6 @@
       <c r="E191" t="n">
         <v>28</v>
       </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>64</t>
@@ -9630,8 +9250,6 @@
       <c r="E192" t="n">
         <v>28</v>
       </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>67</t>
@@ -9678,8 +9296,6 @@
       <c r="E193" t="n">
         <v>28</v>
       </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>70</t>
@@ -9726,8 +9342,6 @@
       <c r="E194" t="n">
         <v>10</v>
       </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
           <t>60</t>
@@ -9774,8 +9388,6 @@
       <c r="E195" t="n">
         <v>10</v>
       </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>63</t>
@@ -9822,8 +9434,6 @@
       <c r="E196" t="n">
         <v>10</v>
       </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>66</t>
@@ -9870,8 +9480,6 @@
       <c r="E197" t="n">
         <v>5</v>
       </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>62</t>
@@ -9918,8 +9526,6 @@
       <c r="E198" t="n">
         <v>5</v>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>65</t>
@@ -9966,8 +9572,6 @@
       <c r="E199" t="n">
         <v>5</v>
       </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>68</t>
@@ -10014,8 +9618,6 @@
       <c r="E200" t="n">
         <v>22</v>
       </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>60</t>
@@ -10062,8 +9664,6 @@
       <c r="E201" t="n">
         <v>22</v>
       </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>63</t>
@@ -10110,8 +9710,6 @@
       <c r="E202" t="n">
         <v>22</v>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>66</t>
@@ -10158,8 +9756,6 @@
       <c r="E203" t="n">
         <v>12</v>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>62</t>
@@ -10206,8 +9802,6 @@
       <c r="E204" t="n">
         <v>12</v>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>65</t>
@@ -10254,8 +9848,6 @@
       <c r="E205" t="n">
         <v>12</v>
       </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>68</t>
@@ -10302,8 +9894,6 @@
       <c r="E206" t="n">
         <v>89</v>
       </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>73</t>
@@ -10350,8 +9940,6 @@
       <c r="E207" t="n">
         <v>89</v>
       </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
           <t>76</t>
@@ -10398,8 +9986,6 @@
       <c r="E208" t="n">
         <v>89</v>
       </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>79</t>
@@ -10446,8 +10032,6 @@
       <c r="E209" t="n">
         <v>91</v>
       </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>78</t>
@@ -10494,8 +10078,6 @@
       <c r="E210" t="n">
         <v>91</v>
       </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>81</t>
@@ -10542,8 +10124,6 @@
       <c r="E211" t="n">
         <v>91</v>
       </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>84</t>
@@ -10587,13 +10167,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -10637,13 +10215,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -10687,13 +10263,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>6:00 AM</t>
@@ -10737,13 +10311,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -10787,13 +10359,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -10837,13 +10407,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -10887,13 +10455,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -10937,13 +10503,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -10987,13 +10551,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
           <t>7:00 AM</t>
@@ -11037,13 +10599,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -11087,13 +10647,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -11137,13 +10695,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -11187,13 +10743,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -11237,13 +10791,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -11287,13 +10839,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -11337,13 +10887,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -11387,13 +10935,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -11437,13 +10983,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -11487,13 +11031,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -11537,13 +11079,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -11587,13 +11127,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -11637,13 +11175,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -11687,13 +11223,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -11737,13 +11271,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -11787,13 +11319,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -11837,13 +11367,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -11887,13 +11415,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -11937,13 +11463,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -11987,13 +11511,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -12037,13 +11559,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -12087,13 +11607,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -12137,13 +11655,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -12187,13 +11703,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -12237,13 +11751,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -12287,13 +11799,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -12337,13 +11847,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -12387,13 +11895,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -12437,13 +11943,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -12487,13 +11991,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -12537,13 +12039,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -12587,13 +12087,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -12637,13 +12135,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -12687,13 +12183,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -12737,13 +12231,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -12787,13 +12279,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -12837,13 +12327,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -12887,13 +12375,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -12937,13 +12423,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -12987,13 +12471,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -13037,13 +12519,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -13087,13 +12567,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -13137,13 +12615,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -13187,13 +12663,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -13237,13 +12711,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -13287,13 +12759,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -13337,13 +12807,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>12:00 PM</t>
@@ -13387,13 +12855,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -13437,13 +12903,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -13487,13 +12951,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -13537,13 +12999,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -13587,13 +13047,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -13637,13 +13095,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -13687,13 +13143,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -13737,13 +13191,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -13787,13 +13239,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -13837,13 +13287,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -13887,13 +13335,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -13937,13 +13383,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -13987,13 +13431,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -14037,13 +13479,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -14087,13 +13527,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -14137,13 +13575,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -14187,13 +13623,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -14237,13 +13671,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -14287,13 +13719,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -14337,13 +13767,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -14387,13 +13815,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -14437,13 +13863,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -14487,13 +13911,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -14537,13 +13959,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -14587,13 +14007,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -14637,13 +14055,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -14687,13 +14103,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -14737,13 +14151,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -14787,13 +14199,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -14837,13 +14247,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -14887,13 +14295,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -14937,13 +14343,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -14987,13 +14391,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -15037,13 +14439,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
           <t>6:00 AM</t>
@@ -15087,13 +14487,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -15137,13 +14535,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -15187,13 +14583,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -15237,13 +14631,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -15287,13 +14679,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>2:00 AM</t>
@@ -15337,13 +14727,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -15387,13 +14775,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -15437,13 +14823,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -15487,13 +14871,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -15537,13 +14919,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -15587,13 +14967,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -15637,13 +15015,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
           <t>2:00 AM</t>
@@ -15687,13 +15063,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -15737,13 +15111,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -15787,13 +15159,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -15837,13 +15207,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
           <t>7:00 AM</t>
@@ -15887,13 +15255,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -15937,13 +15303,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>1:00 PM</t>
@@ -15987,13 +15351,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -16037,13 +15399,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -16087,13 +15447,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -16137,13 +15495,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
           <t>7:00 AM</t>
@@ -16187,13 +15543,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -16237,13 +15591,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -16287,13 +15639,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -16337,13 +15687,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
           <t>12:00 PM</t>
@@ -16387,13 +15735,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -16437,13 +15783,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -16487,13 +15831,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>12:00 PM</t>
@@ -16537,13 +15879,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -16587,13 +15927,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -16637,13 +15975,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -16687,13 +16023,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -16737,13 +16071,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -16787,13 +16119,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>6:00 PM</t>
@@ -16837,13 +16167,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -16887,13 +16215,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -16937,13 +16263,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -16987,13 +16311,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -17037,13 +16359,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -17087,13 +16407,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -17137,13 +16455,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -17187,13 +16503,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -17237,13 +16551,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -17287,13 +16599,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -17337,13 +16647,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -17387,13 +16695,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
           <t>7:00 AM</t>
@@ -17437,13 +16743,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -17487,13 +16791,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -17537,13 +16839,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -17587,13 +16887,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
           <t>13-17 years</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -17637,13 +16935,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -17687,13 +16983,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -17737,13 +17031,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -17787,13 +17079,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -17837,13 +17127,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -17887,13 +17175,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -17937,13 +17223,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -17987,13 +17271,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -18037,13 +17319,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -18087,13 +17367,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -18137,13 +17415,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
           <t>12:00 PM</t>
@@ -18187,13 +17463,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr">
         <is>
           <t>6:00 PM</t>
@@ -18237,13 +17511,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
           <t>3:00 AM</t>
@@ -18287,13 +17559,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -18337,13 +17607,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -18387,13 +17655,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -18437,13 +17703,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -18487,13 +17751,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -18537,13 +17799,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -18587,13 +17847,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr">
         <is>
           <t>6:00 PM</t>
@@ -18637,13 +17895,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -18687,13 +17943,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>28-32 years</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -18737,13 +17991,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>28-32 years</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -18787,13 +18039,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
           <t>28-32 years</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr">
         <is>
           <t>6:00 AM</t>
@@ -18837,13 +18087,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -18887,13 +18135,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -18937,13 +18183,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -18987,13 +18231,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr">
         <is>
           <t>6:00 PM</t>
@@ -19037,13 +18279,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -19087,13 +18327,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -19137,13 +18375,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -19187,13 +18423,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -19237,13 +18471,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -19287,13 +18519,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -19337,13 +18567,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -19387,13 +18615,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
           <t>7-9 years</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -19437,13 +18663,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -19487,13 +18711,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -19537,13 +18759,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
           <t>2:00 AM</t>
@@ -19587,13 +18807,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -19637,13 +18855,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -19687,13 +18903,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
           <t>10-12 years</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -19737,13 +18951,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -19787,13 +18999,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -19837,13 +19047,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -19887,13 +19095,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -19937,13 +19143,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr">
         <is>
           <t>9:00 PM</t>
@@ -19987,13 +19191,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr">
         <is>
           <t>6:00 AM</t>
@@ -20037,13 +19239,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -20087,13 +19287,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -20137,13 +19335,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -20187,13 +19383,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr">
         <is>
           <t>11:00 AM</t>
@@ -20237,13 +19431,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -20287,13 +19479,11 @@
           <t>Appliance</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
           <t>4-6 years</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
           <t>10:00 PM</t>
@@ -20340,7 +19530,6 @@
       <c r="E407" t="n">
         <v>28</v>
       </c>
-      <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20358,7 +19547,7 @@
         <v>1</v>
       </c>
       <c r="K407" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L407" t="n">
         <v>0.2</v>
@@ -20367,7 +19556,7 @@
         <v>1</v>
       </c>
       <c r="N407" t="n">
-        <v>0.76</v>
+        <v>0.7799999999999999</v>
       </c>
     </row>
     <row r="408">
@@ -20392,7 +19581,6 @@
       <c r="E408" t="n">
         <v>28</v>
       </c>
-      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20444,7 +19632,6 @@
       <c r="E409" t="n">
         <v>28</v>
       </c>
-      <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20496,7 +19683,6 @@
       <c r="E410" t="n">
         <v>85</v>
       </c>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20548,7 +19734,6 @@
       <c r="E411" t="n">
         <v>85</v>
       </c>
-      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20600,7 +19785,6 @@
       <c r="E412" t="n">
         <v>85</v>
       </c>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20652,7 +19836,6 @@
       <c r="E413" t="n">
         <v>18</v>
       </c>
-      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20670,16 +19853,16 @@
         <v>0.9</v>
       </c>
       <c r="K413" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="L413" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="414">
@@ -20704,7 +19887,6 @@
       <c r="E414" t="n">
         <v>18</v>
       </c>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20722,16 +19904,16 @@
         <v>0.7</v>
       </c>
       <c r="K414" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L414" t="n">
         <v>0.8</v>
       </c>
       <c r="M414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N414" t="n">
-        <v>0.755</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="415">
@@ -20756,7 +19938,6 @@
       <c r="E415" t="n">
         <v>18</v>
       </c>
-      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -20808,7 +19989,6 @@
       <c r="E416" t="n">
         <v>75</v>
       </c>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>standard</t>
@@ -20860,7 +20040,6 @@
       <c r="E417" t="n">
         <v>75</v>
       </c>
-      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>standard</t>
@@ -20912,7 +20091,6 @@
       <c r="E418" t="n">
         <v>75</v>
       </c>
-      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>standard</t>
@@ -20964,7 +20142,6 @@
       <c r="E419" t="n">
         <v>78</v>
       </c>
-      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21016,7 +20193,6 @@
       <c r="E420" t="n">
         <v>78</v>
       </c>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21031,19 +20207,19 @@
         <v>0.7</v>
       </c>
       <c r="J420" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="K420" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L420" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M420" t="n">
         <v>2</v>
       </c>
       <c r="N420" t="n">
-        <v>0.74</v>
+        <v>0.7474999999999999</v>
       </c>
     </row>
     <row r="421">
@@ -21068,7 +20244,6 @@
       <c r="E421" t="n">
         <v>78</v>
       </c>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21080,13 +20255,13 @@
         </is>
       </c>
       <c r="I421" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J421" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K421" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L421" t="n">
         <v>0.9</v>
@@ -21095,7 +20270,7 @@
         <v>3</v>
       </c>
       <c r="N421" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.7050000000000001</v>
       </c>
     </row>
     <row r="422">
@@ -21120,7 +20295,6 @@
       <c r="E422" t="n">
         <v>28</v>
       </c>
-      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
           <t>standard</t>
@@ -21132,22 +20306,22 @@
         </is>
       </c>
       <c r="I422" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K422" t="n">
         <v>0.7</v>
       </c>
-      <c r="J422" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K422" t="n">
-        <v>0.6</v>
-      </c>
       <c r="L422" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="M422" t="n">
         <v>1</v>
       </c>
       <c r="N422" t="n">
-        <v>0.695</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="423">
@@ -21172,7 +20346,6 @@
       <c r="E423" t="n">
         <v>28</v>
       </c>
-      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>standard</t>
@@ -21224,7 +20397,6 @@
       <c r="E424" t="n">
         <v>28</v>
       </c>
-      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
           <t>standard</t>
@@ -21239,19 +20411,19 @@
         <v>0.3</v>
       </c>
       <c r="J424" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K424" t="n">
         <v>0.9</v>
       </c>
       <c r="L424" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M424" t="n">
         <v>3</v>
       </c>
       <c r="N424" t="n">
-        <v>0.495</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="425">
@@ -21276,7 +20448,6 @@
       <c r="E425" t="n">
         <v>32</v>
       </c>
-      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21294,16 +20465,16 @@
         <v>0.9</v>
       </c>
       <c r="K425" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="L425" t="n">
         <v>0.3</v>
       </c>
       <c r="M425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N425" t="n">
-        <v>0.77</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="426">
@@ -21328,7 +20499,6 @@
       <c r="E426" t="n">
         <v>32</v>
       </c>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21346,16 +20516,16 @@
         <v>0.8</v>
       </c>
       <c r="K426" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L426" t="n">
         <v>0.6</v>
       </c>
       <c r="M426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N426" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="427">
@@ -21380,7 +20550,6 @@
       <c r="E427" t="n">
         <v>32</v>
       </c>
-      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21398,7 +20567,7 @@
         <v>0.6</v>
       </c>
       <c r="K427" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L427" t="n">
         <v>0.9</v>
@@ -21407,7 +20576,7 @@
         <v>3</v>
       </c>
       <c r="N427" t="n">
-        <v>0.7250000000000001</v>
+        <v>0.7050000000000001</v>
       </c>
     </row>
     <row r="428">
@@ -21432,7 +20601,6 @@
       <c r="E428" t="n">
         <v>30</v>
       </c>
-      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21453,13 +20621,13 @@
         <v>0.4</v>
       </c>
       <c r="L428" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M428" t="n">
         <v>3</v>
       </c>
       <c r="N428" t="n">
-        <v>0.7425</v>
+        <v>0.7275</v>
       </c>
     </row>
     <row r="429">
@@ -21484,7 +20652,6 @@
       <c r="E429" t="n">
         <v>30</v>
       </c>
-      <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21499,19 +20666,19 @@
         <v>0.85</v>
       </c>
       <c r="J429" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="K429" t="n">
         <v>0.8</v>
       </c>
       <c r="L429" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M429" t="n">
         <v>1</v>
       </c>
       <c r="N429" t="n">
-        <v>0.8025</v>
+        <v>0.7999999999999999</v>
       </c>
     </row>
     <row r="430">
@@ -21536,7 +20703,6 @@
       <c r="E430" t="n">
         <v>30</v>
       </c>
-      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -21588,7 +20754,6 @@
       <c r="E431" t="n">
         <v>82</v>
       </c>
-      <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
           <t>standard</t>
@@ -21609,13 +20774,13 @@
         <v>0.6</v>
       </c>
       <c r="L431" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M431" t="n">
         <v>1</v>
       </c>
       <c r="N431" t="n">
-        <v>0.7</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="432">
@@ -21640,7 +20805,6 @@
       <c r="E432" t="n">
         <v>82</v>
       </c>
-      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
           <t>standard</t>
@@ -21658,7 +20822,7 @@
         <v>0.6</v>
       </c>
       <c r="K432" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L432" t="n">
         <v>0.7</v>
@@ -21667,7 +20831,7 @@
         <v>2</v>
       </c>
       <c r="N432" t="n">
-        <v>0.675</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="433">
@@ -21692,7 +20856,6 @@
       <c r="E433" t="n">
         <v>82</v>
       </c>
-      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>standard</t>
@@ -21744,7 +20907,6 @@
       <c r="E434" t="n">
         <v>20</v>
       </c>
-      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -21765,13 +20927,13 @@
         <v>0.8</v>
       </c>
       <c r="L434" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M434" t="n">
         <v>1</v>
       </c>
       <c r="N434" t="n">
-        <v>0.655</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="435">
@@ -21796,7 +20958,6 @@
       <c r="E435" t="n">
         <v>20</v>
       </c>
-      <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -21848,7 +21009,6 @@
       <c r="E436" t="n">
         <v>20</v>
       </c>
-      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -21869,13 +21029,13 @@
         <v>1</v>
       </c>
       <c r="L436" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M436" t="n">
         <v>3</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="437">
@@ -21900,7 +21060,6 @@
       <c r="E437" t="n">
         <v>82</v>
       </c>
-      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -21952,7 +21111,6 @@
       <c r="E438" t="n">
         <v>82</v>
       </c>
-      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22004,7 +21162,6 @@
       <c r="E439" t="n">
         <v>82</v>
       </c>
-      <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22025,13 +21182,13 @@
         <v>0.9</v>
       </c>
       <c r="L439" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="M439" t="n">
         <v>3</v>
       </c>
       <c r="N439" t="n">
-        <v>0.29</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="440">
@@ -22056,7 +21213,6 @@
       <c r="E440" t="n">
         <v>30</v>
       </c>
-      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>standard</t>
@@ -22077,13 +21233,13 @@
         <v>0.5</v>
       </c>
       <c r="L440" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M440" t="n">
         <v>1</v>
       </c>
       <c r="N440" t="n">
-        <v>0.74</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="441">
@@ -22108,7 +21264,6 @@
       <c r="E441" t="n">
         <v>30</v>
       </c>
-      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr">
         <is>
           <t>standard</t>
@@ -22160,7 +21315,6 @@
       <c r="E442" t="n">
         <v>30</v>
       </c>
-      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>standard</t>
@@ -22178,16 +21332,16 @@
         <v>0.2</v>
       </c>
       <c r="K442" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L442" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M442" t="n">
         <v>3</v>
       </c>
       <c r="N442" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="443">
@@ -22212,7 +21366,6 @@
       <c r="E443" t="n">
         <v>85</v>
       </c>
-      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
           <t>standard</t>
@@ -22264,7 +21417,6 @@
       <c r="E444" t="n">
         <v>85</v>
       </c>
-      <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
           <t>standard</t>
@@ -22276,22 +21428,22 @@
         </is>
       </c>
       <c r="I444" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="J444" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="K444" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L444" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M444" t="n">
         <v>2</v>
       </c>
       <c r="N444" t="n">
-        <v>0.61</v>
+        <v>0.6375000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -22316,7 +21468,6 @@
       <c r="E445" t="n">
         <v>85</v>
       </c>
-      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr">
         <is>
           <t>standard</t>
@@ -22328,10 +21479,10 @@
         </is>
       </c>
       <c r="I445" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J445" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K445" t="n">
         <v>1</v>
@@ -22343,7 +21494,7 @@
         <v>3</v>
       </c>
       <c r="N445" t="n">
-        <v>0.515</v>
+        <v>0.5800000000000001</v>
       </c>
     </row>
     <row r="446">
@@ -22368,7 +21519,6 @@
       <c r="E446" t="n">
         <v>25</v>
       </c>
-      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22389,13 +21539,13 @@
         <v>0.5</v>
       </c>
       <c r="L446" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M446" t="n">
         <v>1</v>
       </c>
       <c r="N446" t="n">
-        <v>0.71</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="447">
@@ -22420,7 +21570,6 @@
       <c r="E447" t="n">
         <v>25</v>
       </c>
-      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22438,16 +21587,16 @@
         <v>0.5</v>
       </c>
       <c r="K447" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L447" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M447" t="n">
         <v>2</v>
       </c>
       <c r="N447" t="n">
-        <v>0.655</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="448">
@@ -22472,7 +21621,6 @@
       <c r="E448" t="n">
         <v>25</v>
       </c>
-      <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22484,13 +21632,13 @@
         </is>
       </c>
       <c r="I448" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J448" t="n">
         <v>0.2</v>
       </c>
       <c r="K448" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L448" t="n">
         <v>0.5</v>
@@ -22499,7 +21647,7 @@
         <v>3</v>
       </c>
       <c r="N448" t="n">
-        <v>0.435</v>
+        <v>0.3850000000000001</v>
       </c>
     </row>
     <row r="449">
@@ -22524,7 +21672,6 @@
       <c r="E449" t="n">
         <v>90</v>
       </c>
-      <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22536,22 +21683,22 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J449" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="K449" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="L449" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M449" t="n">
         <v>1</v>
       </c>
       <c r="N449" t="n">
-        <v>0.6924999999999999</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="450">
@@ -22576,7 +21723,6 @@
       <c r="E450" t="n">
         <v>90</v>
       </c>
-      <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22588,10 +21734,10 @@
         </is>
       </c>
       <c r="I450" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J450" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K450" t="n">
         <v>0.9</v>
@@ -22603,7 +21749,7 @@
         <v>2</v>
       </c>
       <c r="N450" t="n">
-        <v>0.495</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="451">
@@ -22628,7 +21774,6 @@
       <c r="E451" t="n">
         <v>90</v>
       </c>
-      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22649,13 +21794,13 @@
         <v>1</v>
       </c>
       <c r="L451" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M451" t="n">
         <v>3</v>
       </c>
       <c r="N451" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="452">
@@ -22680,7 +21825,6 @@
       <c r="E452" t="n">
         <v>15</v>
       </c>
-      <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22732,7 +21876,6 @@
       <c r="E453" t="n">
         <v>15</v>
       </c>
-      <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22784,7 +21927,6 @@
       <c r="E454" t="n">
         <v>15</v>
       </c>
-      <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -22836,7 +21978,6 @@
       <c r="E455" t="n">
         <v>78</v>
       </c>
-      <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -22854,16 +21995,16 @@
         <v>0.9</v>
       </c>
       <c r="K455" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L455" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N455" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="456">
@@ -22888,7 +22029,6 @@
       <c r="E456" t="n">
         <v>78</v>
       </c>
-      <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -22906,16 +22046,16 @@
         <v>0.7</v>
       </c>
       <c r="K456" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L456" t="n">
         <v>0.8</v>
       </c>
       <c r="M456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N456" t="n">
-        <v>0.755</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="457">
@@ -22940,7 +22080,6 @@
       <c r="E457" t="n">
         <v>78</v>
       </c>
-      <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -22952,10 +22091,10 @@
         </is>
       </c>
       <c r="I457" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J457" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K457" t="n">
         <v>1</v>
@@ -22967,7 +22106,7 @@
         <v>3</v>
       </c>
       <c r="N457" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="458">
@@ -22992,7 +22131,6 @@
       <c r="E458" t="n">
         <v>88</v>
       </c>
-      <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23004,11 +22142,11 @@
         </is>
       </c>
       <c r="I458" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J458" t="n">
         <v>0.6</v>
       </c>
-      <c r="J458" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K458" t="n">
         <v>0.8</v>
       </c>
@@ -23019,7 +22157,7 @@
         <v>1</v>
       </c>
       <c r="N458" t="n">
-        <v>0.65</v>
+        <v>0.7150000000000001</v>
       </c>
     </row>
     <row r="459">
@@ -23044,7 +22182,6 @@
       <c r="E459" t="n">
         <v>88</v>
       </c>
-      <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23056,7 +22193,7 @@
         </is>
       </c>
       <c r="I459" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="J459" t="n">
         <v>0.4</v>
@@ -23071,7 +22208,7 @@
         <v>2</v>
       </c>
       <c r="N459" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="460">
@@ -23096,7 +22233,6 @@
       <c r="E460" t="n">
         <v>88</v>
       </c>
-      <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23148,7 +22284,6 @@
       <c r="E461" t="n">
         <v>22</v>
       </c>
-      <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -23166,7 +22301,7 @@
         <v>1</v>
       </c>
       <c r="K461" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L461" t="n">
         <v>0.1</v>
@@ -23175,7 +22310,7 @@
         <v>3</v>
       </c>
       <c r="N461" t="n">
-        <v>0.725</v>
+        <v>0.6849999999999999</v>
       </c>
     </row>
     <row r="462">
@@ -23200,7 +22335,6 @@
       <c r="E462" t="n">
         <v>22</v>
       </c>
-      <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -23218,7 +22352,7 @@
         <v>1</v>
       </c>
       <c r="K462" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L462" t="n">
         <v>0.2</v>
@@ -23227,7 +22361,7 @@
         <v>2</v>
       </c>
       <c r="N462" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="463">
@@ -23252,7 +22386,6 @@
       <c r="E463" t="n">
         <v>22</v>
       </c>
-      <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -23270,16 +22403,16 @@
         <v>0.9</v>
       </c>
       <c r="K463" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L463" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M463" t="n">
         <v>1</v>
       </c>
       <c r="N463" t="n">
-        <v>0.77</v>
+        <v>0.7449999999999999</v>
       </c>
     </row>
     <row r="464">
@@ -23304,7 +22437,6 @@
       <c r="E464" t="n">
         <v>80</v>
       </c>
-      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
           <t>standard</t>
@@ -23328,7 +22460,7 @@
         <v>0.2</v>
       </c>
       <c r="M464" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N464" t="n">
         <v>0.7250000000000001</v>
@@ -23356,7 +22488,6 @@
       <c r="E465" t="n">
         <v>80</v>
       </c>
-      <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr">
         <is>
           <t>standard</t>
@@ -23374,16 +22505,16 @@
         <v>0.8</v>
       </c>
       <c r="K465" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L465" t="n">
         <v>0.3</v>
       </c>
       <c r="M465" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N465" t="n">
-        <v>0.7150000000000001</v>
+        <v>0.7350000000000001</v>
       </c>
     </row>
     <row r="466">
@@ -23408,7 +22539,6 @@
       <c r="E466" t="n">
         <v>80</v>
       </c>
-      <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr">
         <is>
           <t>standard</t>
@@ -23460,7 +22590,6 @@
       <c r="E467" t="n">
         <v>12</v>
       </c>
-      <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr">
         <is>
           <t>standard</t>
@@ -23481,13 +22610,13 @@
         <v>0.8</v>
       </c>
       <c r="L467" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M467" t="n">
         <v>1</v>
       </c>
       <c r="N467" t="n">
-        <v>0.625</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="468">
@@ -23512,7 +22641,6 @@
       <c r="E468" t="n">
         <v>12</v>
       </c>
-      <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr">
         <is>
           <t>standard</t>
@@ -23524,10 +22652,10 @@
         </is>
       </c>
       <c r="I468" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J468" t="n">
         <v>0.3</v>
-      </c>
-      <c r="J468" t="n">
-        <v>0.4</v>
       </c>
       <c r="K468" t="n">
         <v>0.9</v>
@@ -23539,7 +22667,7 @@
         <v>2</v>
       </c>
       <c r="N468" t="n">
-        <v>0.53</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="469">
@@ -23564,7 +22692,6 @@
       <c r="E469" t="n">
         <v>12</v>
       </c>
-      <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
           <t>standard</t>
@@ -23616,7 +22743,6 @@
       <c r="E470" t="n">
         <v>92</v>
       </c>
-      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -23637,13 +22763,13 @@
         <v>0.7</v>
       </c>
       <c r="L470" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M470" t="n">
         <v>2</v>
       </c>
       <c r="N470" t="n">
-        <v>0.74</v>
+        <v>0.7549999999999999</v>
       </c>
     </row>
     <row r="471">
@@ -23668,7 +22794,6 @@
       <c r="E471" t="n">
         <v>92</v>
       </c>
-      <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -23720,7 +22845,6 @@
       <c r="E472" t="n">
         <v>92</v>
       </c>
-      <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -23732,10 +22856,10 @@
         </is>
       </c>
       <c r="I472" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J472" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K472" t="n">
         <v>1</v>
@@ -23747,7 +22871,7 @@
         <v>3</v>
       </c>
       <c r="N472" t="n">
-        <v>0.595</v>
+        <v>0.6599999999999999</v>
       </c>
     </row>
     <row r="473">
@@ -23772,7 +22896,6 @@
       <c r="E473" t="n">
         <v>30</v>
       </c>
-      <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23824,7 +22947,6 @@
       <c r="E474" t="n">
         <v>30</v>
       </c>
-      <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23876,7 +22998,6 @@
       <c r="E475" t="n">
         <v>30</v>
       </c>
-      <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23928,7 +23049,6 @@
       <c r="E476" t="n">
         <v>70</v>
       </c>
-      <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23946,7 +23066,7 @@
         <v>0.9</v>
       </c>
       <c r="K476" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L476" t="n">
         <v>0.3</v>
@@ -23955,7 +23075,7 @@
         <v>1</v>
       </c>
       <c r="N476" t="n">
-        <v>0.73</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="477">
@@ -23980,7 +23100,6 @@
       <c r="E477" t="n">
         <v>70</v>
       </c>
-      <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -23998,7 +23117,7 @@
         <v>0.6</v>
       </c>
       <c r="K477" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L477" t="n">
         <v>0.7</v>
@@ -24007,7 +23126,7 @@
         <v>2</v>
       </c>
       <c r="N477" t="n">
-        <v>0.655</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="478">
@@ -24032,7 +23151,6 @@
       <c r="E478" t="n">
         <v>70</v>
       </c>
-      <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -24044,10 +23162,10 @@
         </is>
       </c>
       <c r="I478" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J478" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K478" t="n">
         <v>0.9</v>
@@ -24059,7 +23177,7 @@
         <v>3</v>
       </c>
       <c r="N478" t="n">
-        <v>0.495</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="479">
@@ -24084,7 +23202,6 @@
       <c r="E479" t="n">
         <v>55</v>
       </c>
-      <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -24096,22 +23213,22 @@
         </is>
       </c>
       <c r="I479" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J479" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="K479" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L479" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N479" t="n">
-        <v>0.7124999999999999</v>
+        <v>0.6450000000000001</v>
       </c>
     </row>
     <row r="480">
@@ -24136,7 +23253,6 @@
       <c r="E480" t="n">
         <v>55</v>
       </c>
-      <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -24160,7 +23276,7 @@
         <v>0.7</v>
       </c>
       <c r="M480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N480" t="n">
         <v>0.655</v>
@@ -24188,7 +23304,6 @@
       <c r="E481" t="n">
         <v>55</v>
       </c>
-      <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -24203,7 +23318,7 @@
         <v>0.4</v>
       </c>
       <c r="J481" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K481" t="n">
         <v>0.9</v>
@@ -24215,7 +23330,7 @@
         <v>3</v>
       </c>
       <c r="N481" t="n">
-        <v>0.525</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="482">
@@ -24240,7 +23355,6 @@
       <c r="E482" t="n">
         <v>58</v>
       </c>
-      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24292,7 +23406,6 @@
       <c r="E483" t="n">
         <v>58</v>
       </c>
-      <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24310,7 +23423,7 @@
         <v>0.7</v>
       </c>
       <c r="K483" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L483" t="n">
         <v>0.8</v>
@@ -24319,7 +23432,7 @@
         <v>1</v>
       </c>
       <c r="N483" t="n">
-        <v>0.805</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="484">
@@ -24344,7 +23457,6 @@
       <c r="E484" t="n">
         <v>58</v>
       </c>
-      <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24356,22 +23468,22 @@
         </is>
       </c>
       <c r="I484" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J484" t="n">
         <v>0.3</v>
       </c>
       <c r="K484" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L484" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M484" t="n">
         <v>3</v>
       </c>
       <c r="N484" t="n">
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="485">
@@ -24396,7 +23508,6 @@
       <c r="E485" t="n">
         <v>65</v>
       </c>
-      <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr">
         <is>
           <t>standard</t>
@@ -24417,13 +23528,13 @@
         <v>0.6</v>
       </c>
       <c r="L485" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M485" t="n">
         <v>1</v>
       </c>
       <c r="N485" t="n">
-        <v>0.75</v>
+        <v>0.7424999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -24448,7 +23559,6 @@
       <c r="E486" t="n">
         <v>65</v>
       </c>
-      <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr">
         <is>
           <t>standard</t>
@@ -24469,13 +23579,13 @@
         <v>0.9</v>
       </c>
       <c r="L486" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M486" t="n">
         <v>2</v>
       </c>
       <c r="N486" t="n">
-        <v>0.61</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="487">
@@ -24500,7 +23610,6 @@
       <c r="E487" t="n">
         <v>65</v>
       </c>
-      <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr">
         <is>
           <t>standard</t>
@@ -24552,7 +23661,6 @@
       <c r="E488" t="n">
         <v>50</v>
       </c>
-      <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24573,13 +23681,13 @@
         <v>0.7</v>
       </c>
       <c r="L488" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M488" t="n">
         <v>1</v>
       </c>
       <c r="N488" t="n">
-        <v>0.7549999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="489">
@@ -24604,7 +23712,6 @@
       <c r="E489" t="n">
         <v>50</v>
       </c>
-      <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24656,7 +23763,6 @@
       <c r="E490" t="n">
         <v>50</v>
       </c>
-      <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24677,13 +23783,13 @@
         <v>1</v>
       </c>
       <c r="L490" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="M490" t="n">
         <v>3</v>
       </c>
       <c r="N490" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="491">
@@ -24708,7 +23814,6 @@
       <c r="E491" t="n">
         <v>40</v>
       </c>
-      <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr">
         <is>
           <t>standard</t>
@@ -24760,7 +23865,6 @@
       <c r="E492" t="n">
         <v>40</v>
       </c>
-      <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr">
         <is>
           <t>standard</t>
@@ -24812,7 +23916,6 @@
       <c r="E493" t="n">
         <v>40</v>
       </c>
-      <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr">
         <is>
           <t>standard</t>
@@ -24864,7 +23967,6 @@
       <c r="E494" t="n">
         <v>72</v>
       </c>
-      <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24882,7 +23984,7 @@
         <v>0.85</v>
       </c>
       <c r="K494" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="L494" t="n">
         <v>0.5</v>
@@ -24891,7 +23993,7 @@
         <v>1</v>
       </c>
       <c r="N494" t="n">
-        <v>0.7925</v>
+        <v>0.7865</v>
       </c>
     </row>
     <row r="495">
@@ -24916,7 +24018,6 @@
       <c r="E495" t="n">
         <v>72</v>
       </c>
-      <c r="F495" t="inlineStr"/>
       <c r="G495" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -24968,7 +24069,6 @@
       <c r="E496" t="n">
         <v>72</v>
       </c>
-      <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25020,7 +24120,6 @@
       <c r="E497" t="n">
         <v>52</v>
       </c>
-      <c r="F497" t="inlineStr"/>
       <c r="G497" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25038,16 +24137,16 @@
         <v>0.9</v>
       </c>
       <c r="K497" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L497" t="n">
         <v>0.3</v>
       </c>
       <c r="M497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N497" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="498">
@@ -25072,7 +24171,6 @@
       <c r="E498" t="n">
         <v>52</v>
       </c>
-      <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25090,16 +24188,16 @@
         <v>0.7</v>
       </c>
       <c r="K498" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L498" t="n">
         <v>0.8</v>
       </c>
       <c r="M498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N498" t="n">
-        <v>0.755</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="499">
@@ -25124,7 +24222,6 @@
       <c r="E499" t="n">
         <v>52</v>
       </c>
-      <c r="F499" t="inlineStr"/>
       <c r="G499" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25176,7 +24273,6 @@
       <c r="E500" t="n">
         <v>45</v>
       </c>
-      <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25197,13 +24293,13 @@
         <v>0.6</v>
       </c>
       <c r="L500" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M500" t="n">
         <v>1</v>
       </c>
       <c r="N500" t="n">
-        <v>0.7</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="501">
@@ -25228,7 +24324,6 @@
       <c r="E501" t="n">
         <v>45</v>
       </c>
-      <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25280,7 +24375,6 @@
       <c r="E502" t="n">
         <v>45</v>
       </c>
-      <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25332,7 +24426,6 @@
       <c r="E503" t="n">
         <v>60</v>
       </c>
-      <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25384,7 +24477,6 @@
       <c r="E504" t="n">
         <v>60</v>
       </c>
-      <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25436,7 +24528,6 @@
       <c r="E505" t="n">
         <v>60</v>
       </c>
-      <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -25488,7 +24579,6 @@
       <c r="E506" t="n">
         <v>55</v>
       </c>
-      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25540,7 +24630,6 @@
       <c r="E507" t="n">
         <v>55</v>
       </c>
-      <c r="F507" t="inlineStr"/>
       <c r="G507" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25592,7 +24681,6 @@
       <c r="E508" t="n">
         <v>55</v>
       </c>
-      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25644,7 +24732,6 @@
       <c r="E509" t="n">
         <v>48</v>
       </c>
-      <c r="F509" t="inlineStr"/>
       <c r="G509" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25696,7 +24783,6 @@
       <c r="E510" t="n">
         <v>48</v>
       </c>
-      <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25717,13 +24803,13 @@
         <v>0.9</v>
       </c>
       <c r="L510" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M510" t="n">
         <v>2</v>
       </c>
       <c r="N510" t="n">
-        <v>0.645</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="511">
@@ -25748,7 +24834,6 @@
       <c r="E511" t="n">
         <v>48</v>
       </c>
-      <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25800,7 +24885,6 @@
       <c r="E512" t="n">
         <v>55</v>
       </c>
-      <c r="F512" t="inlineStr"/>
       <c r="G512" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25821,13 +24905,13 @@
         <v>0.9</v>
       </c>
       <c r="L512" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M512" t="n">
         <v>1</v>
       </c>
       <c r="N512" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="513">
@@ -25852,7 +24936,6 @@
       <c r="E513" t="n">
         <v>55</v>
       </c>
-      <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25864,13 +24947,13 @@
         </is>
       </c>
       <c r="I513" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="J513" t="n">
         <v>0.5</v>
       </c>
       <c r="K513" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L513" t="n">
         <v>0.6</v>
@@ -25879,7 +24962,7 @@
         <v>2</v>
       </c>
       <c r="N513" t="n">
-        <v>0.57</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="514">
@@ -25904,7 +24987,6 @@
       <c r="E514" t="n">
         <v>55</v>
       </c>
-      <c r="F514" t="inlineStr"/>
       <c r="G514" t="inlineStr">
         <is>
           <t>standard</t>
@@ -25925,13 +25007,13 @@
         <v>0.9</v>
       </c>
       <c r="L514" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M514" t="n">
         <v>3</v>
       </c>
       <c r="N514" t="n">
-        <v>0.53</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="515">
@@ -25956,7 +25038,6 @@
       <c r="E515" t="n">
         <v>50</v>
       </c>
-      <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26008,7 +25089,6 @@
       <c r="E516" t="n">
         <v>50</v>
       </c>
-      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26026,16 +25106,16 @@
         <v>0.5</v>
       </c>
       <c r="K516" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L516" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M516" t="n">
         <v>2</v>
       </c>
       <c r="N516" t="n">
-        <v>0.585</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="517">
@@ -26060,7 +25140,6 @@
       <c r="E517" t="n">
         <v>50</v>
       </c>
-      <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26075,7 +25154,7 @@
         <v>0.3</v>
       </c>
       <c r="J517" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K517" t="n">
         <v>0.9</v>
@@ -26087,7 +25166,7 @@
         <v>3</v>
       </c>
       <c r="N517" t="n">
-        <v>0.53</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="518">
@@ -26112,7 +25191,6 @@
       <c r="E518" t="n">
         <v>60</v>
       </c>
-      <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26164,7 +25242,6 @@
       <c r="E519" t="n">
         <v>60</v>
       </c>
-      <c r="F519" t="inlineStr"/>
       <c r="G519" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26176,13 +25253,13 @@
         </is>
       </c>
       <c r="I519" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="J519" t="n">
         <v>0.5</v>
       </c>
       <c r="K519" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L519" t="n">
         <v>0.6</v>
@@ -26191,7 +25268,7 @@
         <v>2</v>
       </c>
       <c r="N519" t="n">
-        <v>0.57</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="520">
@@ -26216,7 +25293,6 @@
       <c r="E520" t="n">
         <v>60</v>
       </c>
-      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26234,7 +25310,7 @@
         <v>0.4</v>
       </c>
       <c r="K520" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L520" t="n">
         <v>0.7</v>
@@ -26243,7 +25319,7 @@
         <v>3</v>
       </c>
       <c r="N520" t="n">
-        <v>0.495</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="521">
@@ -26268,7 +25344,6 @@
       <c r="E521" t="n">
         <v>55</v>
       </c>
-      <c r="F521" t="inlineStr"/>
       <c r="G521" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -26320,7 +25395,6 @@
       <c r="E522" t="n">
         <v>55</v>
       </c>
-      <c r="F522" t="inlineStr"/>
       <c r="G522" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -26344,7 +25418,7 @@
         <v>0.8</v>
       </c>
       <c r="M522" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N522" t="n">
         <v>0.625</v>
@@ -26372,7 +25446,6 @@
       <c r="E523" t="n">
         <v>55</v>
       </c>
-      <c r="F523" t="inlineStr"/>
       <c r="G523" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -26384,10 +25457,10 @@
         </is>
       </c>
       <c r="I523" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J523" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K523" t="n">
         <v>1</v>
@@ -26396,10 +25469,10 @@
         <v>0.9</v>
       </c>
       <c r="M523" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N523" t="n">
-        <v>0.595</v>
+        <v>0.6599999999999999</v>
       </c>
     </row>
     <row r="524">
@@ -26424,7 +25497,6 @@
       <c r="E524" t="n">
         <v>58</v>
       </c>
-      <c r="F524" t="inlineStr"/>
       <c r="G524" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26442,16 +25514,16 @@
         <v>0.6</v>
       </c>
       <c r="K524" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L524" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M524" t="n">
         <v>1</v>
       </c>
       <c r="N524" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="525">
@@ -26476,7 +25548,6 @@
       <c r="E525" t="n">
         <v>58</v>
       </c>
-      <c r="F525" t="inlineStr"/>
       <c r="G525" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26494,16 +25565,16 @@
         <v>0.5</v>
       </c>
       <c r="K525" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L525" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="M525" t="n">
         <v>2</v>
       </c>
       <c r="N525" t="n">
-        <v>0.57</v>
+        <v>0.5875</v>
       </c>
     </row>
     <row r="526">
@@ -26528,7 +25599,6 @@
       <c r="E526" t="n">
         <v>58</v>
       </c>
-      <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26580,7 +25650,6 @@
       <c r="E527" t="n">
         <v>10</v>
       </c>
-      <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26632,7 +25701,6 @@
       <c r="E528" t="n">
         <v>10</v>
       </c>
-      <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26653,13 +25721,13 @@
         <v>0.9</v>
       </c>
       <c r="L528" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M528" t="n">
         <v>2</v>
       </c>
       <c r="N528" t="n">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="529">
@@ -26684,7 +25752,6 @@
       <c r="E529" t="n">
         <v>10</v>
       </c>
-      <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26736,7 +25803,6 @@
       <c r="E530" t="n">
         <v>20</v>
       </c>
-      <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -26788,7 +25854,6 @@
       <c r="E531" t="n">
         <v>20</v>
       </c>
-      <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -26840,7 +25905,6 @@
       <c r="E532" t="n">
         <v>20</v>
       </c>
-      <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -26892,7 +25956,6 @@
       <c r="E533" t="n">
         <v>32</v>
       </c>
-      <c r="F533" t="inlineStr"/>
       <c r="G533" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26913,13 +25976,13 @@
         <v>0.6</v>
       </c>
       <c r="L533" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M533" t="n">
+        <v>1</v>
+      </c>
+      <c r="N533" t="n">
         <v>0.7</v>
-      </c>
-      <c r="M533" t="n">
-        <v>1</v>
-      </c>
-      <c r="N533" t="n">
-        <v>0.745</v>
       </c>
     </row>
     <row r="534">
@@ -26944,7 +26007,6 @@
       <c r="E534" t="n">
         <v>32</v>
       </c>
-      <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
           <t>standard</t>
@@ -26996,7 +26058,6 @@
       <c r="E535" t="n">
         <v>32</v>
       </c>
-      <c r="F535" t="inlineStr"/>
       <c r="G535" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27008,7 +26069,7 @@
         </is>
       </c>
       <c r="I535" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J535" t="n">
         <v>0.4</v>
@@ -27017,13 +26078,13 @@
         <v>0.9</v>
       </c>
       <c r="L535" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M535" t="n">
         <v>3</v>
       </c>
       <c r="N535" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="536">
@@ -27048,7 +26109,6 @@
       <c r="E536" t="n">
         <v>92</v>
       </c>
-      <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27100,7 +26160,6 @@
       <c r="E537" t="n">
         <v>92</v>
       </c>
-      <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27152,7 +26211,6 @@
       <c r="E538" t="n">
         <v>92</v>
       </c>
-      <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27204,7 +26262,6 @@
       <c r="E539" t="n">
         <v>42</v>
       </c>
-      <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27225,13 +26282,13 @@
         <v>0.6</v>
       </c>
       <c r="L539" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="M539" t="n">
         <v>1</v>
       </c>
       <c r="N539" t="n">
-        <v>0.7424999999999999</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="540">
@@ -27256,7 +26313,6 @@
       <c r="E540" t="n">
         <v>42</v>
       </c>
-      <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27274,16 +26330,16 @@
         <v>0.7</v>
       </c>
       <c r="K540" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L540" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M540" t="n">
         <v>2</v>
       </c>
       <c r="N540" t="n">
-        <v>0.72</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="541">
@@ -27308,7 +26364,6 @@
       <c r="E541" t="n">
         <v>42</v>
       </c>
-      <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27329,13 +26384,13 @@
         <v>1</v>
       </c>
       <c r="L541" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M541" t="n">
         <v>3</v>
       </c>
       <c r="N541" t="n">
-        <v>0.595</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="542">
@@ -27360,7 +26415,6 @@
       <c r="E542" t="n">
         <v>38</v>
       </c>
-      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -27412,7 +26466,6 @@
       <c r="E543" t="n">
         <v>38</v>
       </c>
-      <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -27464,7 +26517,6 @@
       <c r="E544" t="n">
         <v>38</v>
       </c>
-      <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
           <t>high_flow</t>
@@ -27476,10 +26528,10 @@
         </is>
       </c>
       <c r="I544" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J544" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K544" t="n">
         <v>0.9</v>
@@ -27491,7 +26543,7 @@
         <v>3</v>
       </c>
       <c r="N544" t="n">
-        <v>0.495</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="545">
@@ -27516,7 +26568,6 @@
       <c r="E545" t="n">
         <v>55</v>
       </c>
-      <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -27568,7 +26619,6 @@
       <c r="E546" t="n">
         <v>55</v>
       </c>
-      <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -27589,13 +26639,13 @@
         <v>0.85</v>
       </c>
       <c r="L546" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="M546" t="n">
         <v>1</v>
       </c>
       <c r="N546" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.8174999999999999</v>
       </c>
     </row>
     <row r="547">
@@ -27620,7 +26670,6 @@
       <c r="E547" t="n">
         <v>55</v>
       </c>
-      <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -27672,7 +26721,6 @@
       <c r="E548" t="n">
         <v>62</v>
       </c>
-      <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27724,7 +26772,6 @@
       <c r="E549" t="n">
         <v>62</v>
       </c>
-      <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27742,7 +26789,7 @@
         <v>0.3</v>
       </c>
       <c r="K549" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L549" t="n">
         <v>0.8</v>
@@ -27751,7 +26798,7 @@
         <v>2</v>
       </c>
       <c r="N549" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.5349999999999999</v>
       </c>
     </row>
     <row r="550">
@@ -27776,7 +26823,6 @@
       <c r="E550" t="n">
         <v>62</v>
       </c>
-      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
           <t>standard</t>
@@ -27828,7 +26874,6 @@
       <c r="E551" t="n">
         <v>50</v>
       </c>
-      <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -27880,7 +26925,6 @@
       <c r="E552" t="n">
         <v>50</v>
       </c>
-      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -27932,7 +26976,6 @@
       <c r="E553" t="n">
         <v>50</v>
       </c>
-      <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -27984,7 +27027,6 @@
       <c r="E554" t="n">
         <v>58</v>
       </c>
-      <c r="F554" t="inlineStr"/>
       <c r="G554" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28036,7 +27078,6 @@
       <c r="E555" t="n">
         <v>58</v>
       </c>
-      <c r="F555" t="inlineStr"/>
       <c r="G555" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28088,7 +27129,6 @@
       <c r="E556" t="n">
         <v>58</v>
       </c>
-      <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28103,7 +27143,7 @@
         <v>0.4</v>
       </c>
       <c r="J556" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K556" t="n">
         <v>1</v>
@@ -28115,7 +27155,7 @@
         <v>3</v>
       </c>
       <c r="N556" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.5449999999999999</v>
       </c>
     </row>
     <row r="557">
@@ -28140,7 +27180,6 @@
       <c r="E557" t="n">
         <v>55</v>
       </c>
-      <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28192,7 +27231,6 @@
       <c r="E558" t="n">
         <v>55</v>
       </c>
-      <c r="F558" t="inlineStr"/>
       <c r="G558" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28244,7 +27282,6 @@
       <c r="E559" t="n">
         <v>55</v>
       </c>
-      <c r="F559" t="inlineStr"/>
       <c r="G559" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28265,13 +27302,13 @@
         <v>1</v>
       </c>
       <c r="L559" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M559" t="n">
         <v>3</v>
       </c>
       <c r="N559" t="n">
-        <v>0.61</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="560">
@@ -28296,7 +27333,6 @@
       <c r="E560" t="n">
         <v>58</v>
       </c>
-      <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28348,7 +27384,6 @@
       <c r="E561" t="n">
         <v>58</v>
       </c>
-      <c r="F561" t="inlineStr"/>
       <c r="G561" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28366,7 +27401,7 @@
         <v>0.5</v>
       </c>
       <c r="K561" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L561" t="n">
         <v>0.6</v>
@@ -28375,7 +27410,7 @@
         <v>2</v>
       </c>
       <c r="N561" t="n">
-        <v>0.585</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="562">
@@ -28400,7 +27435,6 @@
       <c r="E562" t="n">
         <v>58</v>
       </c>
-      <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28452,7 +27486,6 @@
       <c r="E563" t="n">
         <v>5</v>
       </c>
-      <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -28470,16 +27503,16 @@
         <v>0.9</v>
       </c>
       <c r="K563" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L563" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M563" t="n">
         <v>1</v>
       </c>
       <c r="N563" t="n">
-        <v>0.7349999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="564">
@@ -28504,7 +27537,6 @@
       <c r="E564" t="n">
         <v>5</v>
       </c>
-      <c r="F564" t="inlineStr"/>
       <c r="G564" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -28516,10 +27548,10 @@
         </is>
       </c>
       <c r="I564" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="J564" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="K564" t="n">
         <v>0.9</v>
@@ -28531,7 +27563,7 @@
         <v>2</v>
       </c>
       <c r="N564" t="n">
-        <v>0.7225</v>
+        <v>0.6900000000000001</v>
       </c>
     </row>
     <row r="565">
@@ -28556,7 +27588,6 @@
       <c r="E565" t="n">
         <v>5</v>
       </c>
-      <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -28608,7 +27639,6 @@
       <c r="E566" t="n">
         <v>65</v>
       </c>
-      <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -28626,16 +27656,16 @@
         <v>1</v>
       </c>
       <c r="K566" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L566" t="n">
         <v>0.2</v>
       </c>
       <c r="M566" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N566" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="567">
@@ -28660,7 +27690,6 @@
       <c r="E567" t="n">
         <v>65</v>
       </c>
-      <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -28678,16 +27707,16 @@
         <v>0.9</v>
       </c>
       <c r="K567" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L567" t="n">
         <v>0.3</v>
       </c>
       <c r="M567" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N567" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="568">
@@ -28712,7 +27741,6 @@
       <c r="E568" t="n">
         <v>65</v>
       </c>
-      <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -28730,7 +27758,7 @@
         <v>0.7</v>
       </c>
       <c r="K568" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L568" t="n">
         <v>0.8</v>
@@ -28739,7 +27767,7 @@
         <v>1</v>
       </c>
       <c r="N568" t="n">
-        <v>0.805</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="569">
@@ -28764,7 +27792,6 @@
       <c r="E569" t="n">
         <v>78</v>
       </c>
-      <c r="F569" t="inlineStr"/>
       <c r="G569" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28816,7 +27843,6 @@
       <c r="E570" t="n">
         <v>78</v>
       </c>
-      <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28868,7 +27894,6 @@
       <c r="E571" t="n">
         <v>78</v>
       </c>
-      <c r="F571" t="inlineStr"/>
       <c r="G571" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28920,7 +27945,6 @@
       <c r="E572" t="n">
         <v>72</v>
       </c>
-      <c r="F572" t="inlineStr"/>
       <c r="G572" t="inlineStr">
         <is>
           <t>standard</t>
@@ -28972,7 +27996,6 @@
       <c r="E573" t="n">
         <v>72</v>
       </c>
-      <c r="F573" t="inlineStr"/>
       <c r="G573" t="inlineStr">
         <is>
           <t>standard</t>
@@ -29024,7 +28047,6 @@
       <c r="E574" t="n">
         <v>72</v>
       </c>
-      <c r="F574" t="inlineStr"/>
       <c r="G574" t="inlineStr">
         <is>
           <t>standard</t>
@@ -29076,7 +28098,6 @@
       <c r="E575" t="n">
         <v>58</v>
       </c>
-      <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29094,7 +28115,7 @@
         <v>1</v>
       </c>
       <c r="K575" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L575" t="n">
         <v>0.2</v>
@@ -29103,7 +28124,7 @@
         <v>2</v>
       </c>
       <c r="N575" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="576">
@@ -29128,7 +28149,6 @@
       <c r="E576" t="n">
         <v>58</v>
       </c>
-      <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29146,7 +28166,7 @@
         <v>0.9</v>
       </c>
       <c r="K576" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L576" t="n">
         <v>0.3</v>
@@ -29155,7 +28175,7 @@
         <v>3</v>
       </c>
       <c r="N576" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="577">
@@ -29180,7 +28200,6 @@
       <c r="E577" t="n">
         <v>58</v>
       </c>
-      <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29198,7 +28217,7 @@
         <v>0.7</v>
       </c>
       <c r="K577" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L577" t="n">
         <v>0.8</v>
@@ -29207,7 +28226,7 @@
         <v>1</v>
       </c>
       <c r="N577" t="n">
-        <v>0.785</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="578">
@@ -29232,7 +28251,6 @@
       <c r="E578" t="n">
         <v>35</v>
       </c>
-      <c r="F578" t="inlineStr"/>
       <c r="G578" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29256,7 +28274,7 @@
         <v>0.25</v>
       </c>
       <c r="M578" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N578" t="n">
         <v>0.76</v>
@@ -29284,7 +28302,6 @@
       <c r="E579" t="n">
         <v>35</v>
       </c>
-      <c r="F579" t="inlineStr"/>
       <c r="G579" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29296,7 +28313,7 @@
         </is>
       </c>
       <c r="I579" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J579" t="n">
         <v>0.85</v>
@@ -29305,13 +28322,13 @@
         <v>0.75</v>
       </c>
       <c r="L579" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M579" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N579" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="580">
@@ -29336,7 +28353,6 @@
       <c r="E580" t="n">
         <v>35</v>
       </c>
-      <c r="F580" t="inlineStr"/>
       <c r="G580" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29388,7 +28404,6 @@
       <c r="E581" t="n">
         <v>45</v>
       </c>
-      <c r="F581" t="inlineStr"/>
       <c r="G581" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29406,16 +28421,16 @@
         <v>0.95</v>
       </c>
       <c r="K581" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="L581" t="n">
         <v>0.25</v>
       </c>
       <c r="M581" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N581" t="n">
-        <v>0.7749999999999999</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="582">
@@ -29440,7 +28455,6 @@
       <c r="E582" t="n">
         <v>45</v>
       </c>
-      <c r="F582" t="inlineStr"/>
       <c r="G582" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29458,16 +28472,16 @@
         <v>0.85</v>
       </c>
       <c r="K582" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="L582" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M582" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N582" t="n">
-        <v>0.77</v>
+        <v>0.7474999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -29492,7 +28506,6 @@
       <c r="E583" t="n">
         <v>45</v>
       </c>
-      <c r="F583" t="inlineStr"/>
       <c r="G583" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29510,7 +28523,7 @@
         <v>0.6</v>
       </c>
       <c r="K583" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L583" t="n">
         <v>0.9</v>
@@ -29519,7 +28532,7 @@
         <v>3</v>
       </c>
       <c r="N583" t="n">
-        <v>0.7250000000000001</v>
+        <v>0.7050000000000001</v>
       </c>
     </row>
     <row r="584">
@@ -29544,7 +28557,6 @@
       <c r="E584" t="n">
         <v>42</v>
       </c>
-      <c r="F584" t="inlineStr"/>
       <c r="G584" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29562,7 +28574,7 @@
         <v>1</v>
       </c>
       <c r="K584" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L584" t="n">
         <v>0.2</v>
@@ -29571,7 +28583,7 @@
         <v>1</v>
       </c>
       <c r="N584" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="585">
@@ -29596,7 +28608,6 @@
       <c r="E585" t="n">
         <v>42</v>
       </c>
-      <c r="F585" t="inlineStr"/>
       <c r="G585" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29614,16 +28625,16 @@
         <v>0.9</v>
       </c>
       <c r="K585" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L585" t="n">
         <v>0.3</v>
       </c>
       <c r="M585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N585" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="586">
@@ -29648,7 +28659,6 @@
       <c r="E586" t="n">
         <v>42</v>
       </c>
-      <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr">
         <is>
           <t>low_flow</t>
@@ -29666,16 +28676,16 @@
         <v>0.7</v>
       </c>
       <c r="K586" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L586" t="n">
         <v>0.8</v>
       </c>
       <c r="M586" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N586" t="n">
-        <v>0.755</v>
+        <v>0.735</v>
       </c>
     </row>
   </sheetData>
